--- a/lab5/out/lab5_unit_economics.xlsx
+++ b/lab5/out/lab5_unit_economics.xlsx
@@ -3442,9 +3442,9 @@
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12.5" customWidth="1" min="17" max="17"/>
+    <col width="12.5" customWidth="1" min="18" max="18"/>
     <col width="2" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="11" customWidth="1" min="21" max="21"/>
@@ -4896,15 +4896,15 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>(x5_rev_bu*B$2+x5_over)/x5_clients</f>
+        <f>(x5_rev_bu+x5_over)*B$2/x5_clients</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>(x5_rev_bu*C$2+x5_over)/x5_clients</f>
+        <f>(x5_rev_bu+x5_over)*C$2/x5_clients</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>(x5_rev_bu*D$2+x5_over)/x5_clients</f>
+        <f>(x5_rev_bu+x5_over)*D$2/x5_clients</f>
         <v/>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -5227,7 +5227,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Припущення для ціни: COGS на акаунт 34,83 EUR і overage 467,5 EUR незмінні; змінюються базовий платіж і ціна будівлі; інші змінні витрати 6% від нової ARPA.</t>
+          <t>Припущення для ціни: змінюються всі ціни прайсу (базовий платіж, ціна будівлі, ставка overage 55 EUR); COGS на акаунт 34,83 EUR незмінний; інші змінні витрати 6% від нової ARPA.</t>
         </is>
       </c>
     </row>

--- a/lab5/out/lab5_unit_economics.xlsx
+++ b/lab5/out/lab5_unit_economics.xlsx
@@ -80,7 +80,8 @@
     <definedName name="x5_be_p_b">'Break-even'!$D$11</definedName>
     <definedName name="x5_be_o_b">'Break-even'!$D$12</definedName>
     <definedName name="x5_be_mos">'Break-even'!$D$13</definedName>
-    <definedName name="x5_be_steady">'Break-even'!$D$14</definedName>
+    <definedName name="x5_be_mos_o">'Break-even'!$D$14</definedName>
+    <definedName name="x5_be_steady">'Break-even'!$D$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -217,6 +218,9 @@
     <xf numFmtId="10" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -233,9 +237,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1066,8 +1067,9 @@
           <t>Revenue базового місяця Y3</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>11567.5</v>
+      <c r="C7" s="6">
+        <f>x5_rev_bu+x5_over</f>
+        <v/>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -1076,12 +1078,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Д</t>
+          <t>Р</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>ЛР № 4, сценарій 100%</t>
+          <t>ЛР № 4, сценарій 100%: сума двох рядків нижче</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1188,7 @@
           <t>Активні клієнти (акаунти) Y3</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="7" t="n">
         <v>50</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1216,7 +1218,7 @@
           <t>Будівель на клієнта</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="7" t="n">
         <v>1.7</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1276,7 +1278,7 @@
           <t>Епізод нестабільного обліку</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1426,7 +1428,7 @@
           <t>Тривалість пілоту</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <v>3</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1456,7 +1458,7 @@
           <t>Місяць відсіву пілотів</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1606,7 +1608,7 @@
           <t>Горизонт обмеженого LTV</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="7" t="n">
         <v>36</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1636,7 +1638,7 @@
           <t>Горизонт прогнозу</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="7" t="n">
         <v>12</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1704,7 +1706,7 @@
           <t>Змінні витрати поза COGS, частка</t>
         </is>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>x5_pay+x5_bad+x5_partner</f>
         <v/>
       </c>
@@ -1735,7 +1737,7 @@
           <t>Місячна ставка дисконтування</t>
         </is>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="9">
         <f>(1+x5_disc)^(1/12)-1</f>
         <v/>
       </c>
@@ -2134,11 +2136,11 @@
           <t>кваліфікований лід: дзвінок з розрахунком економії відбувся</t>
         </is>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="10">
         <f>x5_leads</f>
         <v/>
       </c>
-      <c r="D2" s="10" t="inlineStr"/>
+      <c r="D2" s="11" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>B1 (П)</t>
@@ -2156,11 +2158,11 @@
           <t>пілот запущено: шлюз передав першу добу 15-хв даних</t>
         </is>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="10">
         <f>C2*x5_act</f>
         <v/>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="12">
         <f>C3/C2</f>
         <v/>
       </c>
@@ -2181,11 +2183,11 @@
           <t>пілот активний у 3-му місяці: реакція на алерт підтверджена</t>
         </is>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="10">
         <f>x5_kept</f>
         <v/>
       </c>
-      <c r="D4" s="11">
+      <c r="D4" s="12">
         <f>C4/C3</f>
         <v/>
       </c>
@@ -2206,11 +2208,11 @@
           <t>перший оплачений рахунок (новий платний клієнт)</t>
         </is>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="10">
         <f>x5_new</f>
         <v/>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="12">
         <f>C5/C4</f>
         <v/>
       </c>
@@ -2248,7 +2250,7 @@
           <t>Revenue / Acquisition</t>
         </is>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="12">
         <f>C5/C2</f>
         <v/>
       </c>
@@ -2264,7 +2266,7 @@
           <t>Revenue / Activation</t>
         </is>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <f>C5/C3</f>
         <v/>
       </c>
@@ -2280,7 +2282,7 @@
           <t>пілоти × 1 + утримані × (3 − 1)</t>
         </is>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="10">
         <f>C3*x5_check+C4*(x5_pilot_m-x5_check)</f>
         <v/>
       </c>
@@ -2296,7 +2298,7 @@
           <t>буд.-міс. × COGS 16</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="6">
         <f>C10*x5_cogs_unit</f>
         <v/>
       </c>
@@ -2312,7 +2314,7 @@
           <t>B5</t>
         </is>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="6">
         <f>x5_events</f>
         <v/>
       </c>
@@ -2328,7 +2330,7 @@
           <t>spend − пілоти − події</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="6">
         <f>x5_spend-C11-C12</f>
         <v/>
       </c>
@@ -2344,7 +2346,7 @@
           <t>сума</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="6">
         <f>C11+C12+C13</f>
         <v/>
       </c>
@@ -2360,7 +2362,7 @@
           <t>spend / ліди</t>
         </is>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="6">
         <f>x5_spend/C2</f>
         <v/>
       </c>
@@ -2376,7 +2378,7 @@
           <t>spend / пілоти</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="6">
         <f>x5_spend/C3</f>
         <v/>
       </c>
@@ -2446,7 +2448,7 @@
           <t>acquisition spend / нові платні клієнти</t>
         </is>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="6">
         <f>x5_spend/x5_new</f>
         <v/>
       </c>
@@ -2472,7 +2474,7 @@
           <t>Revenue / активні акаунти</t>
         </is>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="6">
         <f>x5_rev/x5_clients</f>
         <v/>
       </c>
@@ -2498,7 +2500,7 @@
           <t>Revenue / будівлі (не змішується з ARPA)</t>
         </is>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="6">
         <f>x5_rev/x5_scale</f>
         <v/>
       </c>
@@ -2524,7 +2526,7 @@
           <t>COGS / активні акаунти</t>
         </is>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="6">
         <f>x5_cogs/x5_clients</f>
         <v/>
       </c>
@@ -2550,7 +2552,7 @@
           <t>ARPA − COGS на акаунт</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <f>x5_arpa-x5_cogs_pa</f>
         <v/>
       </c>
@@ -2576,7 +2578,7 @@
           <t>(Revenue − COGS) / Revenue</t>
         </is>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>(x5_rev-x5_cogs)/x5_rev</f>
         <v/>
       </c>
@@ -2602,7 +2604,7 @@
           <t>ARPA × 6%</t>
         </is>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <f>x5_arpa*x5_ovshare</f>
         <v/>
       </c>
@@ -2628,7 +2630,7 @@
           <t>ARPA − COGS − інші змінні</t>
         </is>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <f>x5_arpa-x5_cogs_pa-x5_ov</f>
         <v/>
       </c>
@@ -2654,7 +2656,7 @@
           <t>CM / ARPA</t>
         </is>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>x5_cm/x5_arpa</f>
         <v/>
       </c>
@@ -2706,7 +2708,7 @@
           <t>churn × MRR на початок (B7)</t>
         </is>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="6">
         <f>x5_churn*x5_rev</f>
         <v/>
       </c>
@@ -2732,7 +2734,7 @@
           <t>overage / 12</t>
         </is>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="6">
         <f>x5_over/x5_episode</f>
         <v/>
       </c>
@@ -2758,7 +2760,7 @@
           <t>дорівнює скороченню (B7)</t>
         </is>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="6">
         <f>x5_contr</f>
         <v/>
       </c>
@@ -2836,7 +2838,7 @@
           <t>ARPA × GM / logo churn</t>
         </is>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="6">
         <f>x5_arpa*x5_gm/x5_churn</f>
         <v/>
       </c>
@@ -2940,7 +2942,7 @@
           <t>CM / logo churn</t>
         </is>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="6">
         <f>x5_cm/x5_churn</f>
         <v/>
       </c>
@@ -2966,7 +2968,7 @@
           <t>GP / gross revenue churn</t>
         </is>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="6">
         <f>x5_gp/x5_grc</f>
         <v/>
       </c>
@@ -2992,7 +2994,7 @@
           <t>GP × (1 + d) / (churn + d)</t>
         </is>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="6">
         <f>x5_gp*(1+x5_dm)/(x5_churn+x5_dm)</f>
         <v/>
       </c>
@@ -3018,7 +3020,7 @@
           <t>GP × (1 − (1 − churn)^36) / churn</t>
         </is>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="6">
         <f>x5_gp*(1-(1-x5_churn)^x5_cap)/x5_churn</f>
         <v/>
       </c>
@@ -3066,7 +3068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3113,7 +3115,7 @@
           <t>CM на акаунт (одиниця BE: активний клієнт)</t>
         </is>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="6">
         <f>x5_cm</f>
         <v/>
       </c>
@@ -3134,7 +3136,7 @@
           <t>варіант 14, EUR на місяць</t>
         </is>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="6">
         <f>x5_fixed</f>
         <v/>
       </c>
@@ -3155,7 +3157,7 @@
           <t>варіант 14, EUR на місяць, B10</t>
         </is>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="6">
         <f>x5_spend</f>
         <v/>
       </c>
@@ -3197,7 +3199,7 @@
           <t>ROUNDUP</t>
         </is>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <f>ROUNDUP(x5_be_p-1E-9,0)</f>
         <v/>
       </c>
@@ -3239,7 +3241,7 @@
           <t>ROUNDUP</t>
         </is>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <f>ROUNDUP(x5_be_o-1E-9,0)</f>
         <v/>
       </c>
@@ -3260,7 +3262,7 @@
           <t>fixed OPEX / CM ratio</t>
         </is>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <f>x5_be_fixed/x5_cmr</f>
         <v/>
       </c>
@@ -3281,7 +3283,7 @@
           <t>(fixed OPEX + spend) / CM ratio</t>
         </is>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="6">
         <f>(x5_be_fixed+x5_be_acq)/x5_cmr</f>
         <v/>
       </c>
@@ -3336,15 +3338,15 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Запас Y3 ЛР № 4 над product BE</t>
+          <t>Запас безпеки Y3 ЛР № 4 над product BE</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>(50 − BE) / 50</t>
-        </is>
-      </c>
-      <c r="D13" s="7">
+          <t>(клієнти Y3 − BE) / клієнти Y3</t>
+        </is>
+      </c>
+      <c r="D13" s="8">
         <f>(x5_clients-x5_be_p)/x5_clients</f>
         <v/>
       </c>
@@ -3352,62 +3354,83 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>x5_be_steady</t>
+          <t>x5_be_mos_o</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Стаціонарна база клієнтів</t>
+          <t>Запас безпеки M12 над operating BE</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>нові / churn</t>
-        </is>
-      </c>
-      <c r="D14" s="13">
-        <f>x5_new/x5_churn</f>
+          <t>(клієнти M12 − BE) / клієнти M12</t>
+        </is>
+      </c>
+      <c r="D14" s="8">
+        <f>('Прогноз 12 міс.'!$F$13-x5_be_o)/'Прогноз 12 міс.'!$F$13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>x5_m_p</t>
+          <t>x5_be_steady</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Перший місяць product BE</t>
+          <t>Стаціонарна база клієнтів</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>аркуш «Прогноз 12 міс.»</t>
-        </is>
-      </c>
-      <c r="D15" s="15">
-        <f>'Прогноз 12 міс.'!$F$16</f>
+          <t>нові / churn</t>
+        </is>
+      </c>
+      <c r="D15" s="13">
+        <f>x5_new/x5_churn</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>x5_m_p</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Перший місяць product BE</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>аркуш «Прогноз 12 міс.»</t>
+        </is>
+      </c>
+      <c r="D16" s="15">
+        <f>'Прогноз 12 міс.'!$F$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
           <t>x5_m_o</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Перший місяць operating BE</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>аркуш «Прогноз 12 міс.»</t>
         </is>
       </c>
-      <c r="D16" s="15">
+      <c r="D17" s="15">
         <f>'Прогноз 12 міс.'!$F$17</f>
         <v/>
       </c>
@@ -4760,15 +4783,15 @@
           <t>Monthly logo churn</t>
         </is>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <f>x5_churn*B$2</f>
         <v/>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <f>x5_churn*C$2</f>
         <v/>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <f>x5_churn*D$2</f>
         <v/>
       </c>
@@ -4780,15 +4803,15 @@
           <t>Просте LTV, EUR</t>
         </is>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="6">
         <f>x5_arpa*x5_gm/B4</f>
         <v/>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="6">
         <f>x5_arpa*x5_gm/C4</f>
         <v/>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="6">
         <f>x5_arpa*x5_gm/D4</f>
         <v/>
       </c>
@@ -4840,15 +4863,15 @@
           <t>Місяць product BE</t>
         </is>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="10">
         <f>IF(x5_be_p&gt;=x5_new/B4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_p*B4/x5_new)/LN(1-B4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_p*B4/x5_new)/LN(1-B4)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>IF(x5_be_p&gt;=x5_new/C4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_p*C4/x5_new)/LN(1-C4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_p*C4/x5_new)/LN(1-C4)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="10">
         <f>IF(x5_be_p&gt;=x5_new/D4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_p*D4/x5_new)/LN(1-D4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_p*D4/x5_new)/LN(1-D4)-1E-9,0)))</f>
         <v/>
       </c>
@@ -4860,15 +4883,15 @@
           <t>Місяць operating BE</t>
         </is>
       </c>
-      <c r="B9" s="9">
+      <c r="B9" s="10">
         <f>IF(x5_be_o&gt;=x5_new/B4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_o*B4/x5_new)/LN(1-B4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_o*B4/x5_new)/LN(1-B4)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>IF(x5_be_o&gt;=x5_new/C4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_o*C4/x5_new)/LN(1-C4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_o*C4/x5_new)/LN(1-C4)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="10">
         <f>IF(x5_be_o&gt;=x5_new/D4,"не досягнуто",IF(ROUNDUP(LN(1-x5_be_o*D4/x5_new)/LN(1-D4)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-x5_be_o*D4/x5_new)/LN(1-D4)-1E-9,0)))</f>
         <v/>
       </c>
@@ -4895,15 +4918,15 @@
           <t>ARPA, EUR</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="6">
         <f>(x5_rev_bu+x5_over)*B$2/x5_clients</f>
         <v/>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="6">
         <f>(x5_rev_bu+x5_over)*C$2/x5_clients</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="6">
         <f>(x5_rev_bu+x5_over)*D$2/x5_clients</f>
         <v/>
       </c>
@@ -4915,15 +4938,15 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>(B11-x5_cogs_pa)/B11</f>
         <v/>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>(C11-x5_cogs_pa)/C11</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>(D11-x5_cogs_pa)/D11</f>
         <v/>
       </c>
@@ -4935,15 +4958,15 @@
           <t>CM на акаунт, EUR</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="6">
         <f>B11*(1-x5_ovshare)-x5_cogs_pa</f>
         <v/>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="6">
         <f>C11*(1-x5_ovshare)-x5_cogs_pa</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="6">
         <f>D11*(1-x5_ovshare)-x5_cogs_pa</f>
         <v/>
       </c>
@@ -4955,15 +4978,15 @@
           <t>Просте LTV, EUR</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="6">
         <f>B11*B12/x5_churn</f>
         <v/>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="6">
         <f>C11*C12/x5_churn</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="6">
         <f>D11*D12/x5_churn</f>
         <v/>
       </c>
@@ -5035,15 +5058,15 @@
           <t>Місяць product BE</t>
         </is>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="10">
         <f>IF(B16&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-B16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-B16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="10">
         <f>IF(C16&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-C16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-C16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="10">
         <f>IF(D16&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-D16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-D16*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
@@ -5055,15 +5078,15 @@
           <t>Місяць operating BE</t>
         </is>
       </c>
-      <c r="B19" s="9">
+      <c r="B19" s="10">
         <f>IF(B17&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-B17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-B17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="10">
         <f>IF(C17&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-C17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-C17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="10">
         <f>IF(D17&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-D17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-D17*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
@@ -5090,15 +5113,15 @@
           <t>Acquisition spend, EUR</t>
         </is>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="6">
         <f>x5_spend*B$2</f>
         <v/>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="6">
         <f>x5_spend*C$2</f>
         <v/>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="6">
         <f>x5_spend*D$2</f>
         <v/>
       </c>
@@ -5110,15 +5133,15 @@
           <t>CAC, EUR</t>
         </is>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="6">
         <f>B21/x5_new</f>
         <v/>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="6">
         <f>C21/x5_new</f>
         <v/>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="6">
         <f>D21/x5_new</f>
         <v/>
       </c>
@@ -5210,15 +5233,15 @@
           <t>Місяць operating BE</t>
         </is>
       </c>
-      <c r="B27" s="9">
+      <c r="B27" s="10">
         <f>IF(B26&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-B26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-B26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="C27" s="9">
+      <c r="C27" s="10">
         <f>IF(C26&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-C26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-C26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="10">
         <f>IF(D26&gt;=x5_new/x5_churn,"не досягнуто",IF(ROUNDUP(LN(1-D26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)&gt;x5_h,"не досягнуто",ROUNDUP(LN(1-D26*x5_churn/x5_new)/LN(1-x5_churn)-1E-9,0)))</f>
         <v/>
       </c>

--- a/lab5/out/lab5_unit_economics.xlsx
+++ b/lab5/out/lab5_unit_economics.xlsx
@@ -81,7 +81,9 @@
     <definedName name="x5_be_o_b">'Break-even'!$D$12</definedName>
     <definedName name="x5_be_mos">'Break-even'!$D$13</definedName>
     <definedName name="x5_be_mos_o">'Break-even'!$D$14</definedName>
-    <definedName name="x5_be_steady">'Break-even'!$D$15</definedName>
+    <definedName name="x5_mos_oy3">'Break-even'!$D$15</definedName>
+    <definedName name="x5_fix_room">'Break-even'!$D$16</definedName>
+    <definedName name="x5_be_steady">'Break-even'!$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3068,7 +3070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3375,62 +3377,104 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>x5_be_steady</t>
+          <t>x5_mos_oy3</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Стаціонарна база клієнтів</t>
+          <t>Запас безпеки Y3 ЛР № 4 над operating BE</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>нові / churn</t>
-        </is>
-      </c>
-      <c r="D15" s="13">
-        <f>x5_new/x5_churn</f>
+          <t>(клієнти Y3 − BE) / клієнти Y3</t>
+        </is>
+      </c>
+      <c r="D15" s="8">
+        <f>(x5_clients-x5_be_o)/x5_clients</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>x5_m_p</t>
+          <t>x5_fix_room</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Перший місяць product BE</t>
+          <t>Допустимий приріст fixed OPEX для operating BE у M12</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>аркуш «Прогноз 12 міс.»</t>
-        </is>
-      </c>
-      <c r="D16" s="15">
-        <f>'Прогноз 12 міс.'!$F$16</f>
+          <t>(клієнти M12 − operating BE) × CM, EUR на місяць</t>
+        </is>
+      </c>
+      <c r="D16" s="6">
+        <f>('Прогноз 12 міс.'!$F$13-x5_be_o)*x5_be_cm</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>x5_be_steady</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Стаціонарна база клієнтів</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>нові / churn</t>
+        </is>
+      </c>
+      <c r="D17" s="13">
+        <f>x5_new/x5_churn</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>x5_m_p</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Перший місяць product BE</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>аркуш «Прогноз 12 міс.»</t>
+        </is>
+      </c>
+      <c r="D18" s="15">
+        <f>'Прогноз 12 міс.'!$F$16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>x5_m_o</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Перший місяць operating BE</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>аркуш «Прогноз 12 міс.»</t>
         </is>
       </c>
-      <c r="D17" s="15">
+      <c r="D19" s="15">
         <f>'Прогноз 12 міс.'!$F$17</f>
         <v/>
       </c>
